--- a/3-能力管理/运行记录类文件/030204-2025年1-10月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年1-10月运维服务能力改进计划及跟踪.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t xml:space="preserve">
 2025年运维服务能力改进计划及跟踪</t>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>改进结果跟踪</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>待改进过程/活动</t>
@@ -121,6 +118,9 @@
   </si>
   <si>
     <t>跟踪中</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
   <si>
     <t>客户满意度调查结果分析</t>
@@ -204,12 +204,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -349,6 +343,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -740,57 +740,57 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -818,14 +818,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -1181,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
@@ -1192,10 +1184,9 @@
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1" spans="1:11">
+    <row r="1" ht="41.25" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1208,9 +1199,8 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
     </row>
-    <row r="2" ht="26.25" customHeight="1" spans="1:11">
+    <row r="2" ht="26.25" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1229,146 +1219,138 @@
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" ht="26.25" customHeight="1" spans="1:11">
+    <row r="3" ht="26.25" customHeight="1" spans="1:10">
       <c r="A3" s="3"/>
       <c r="B3" s="8"/>
       <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="3"/>
     </row>
-    <row r="4" ht="130" customHeight="1" spans="1:11">
+    <row r="4" ht="130" customHeight="1" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="3" t="s">
+    </row>
+    <row r="5" ht="48" spans="1:10">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="3">
+        <v>46021</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" ht="57.6" spans="1:11">
-      <c r="A5" s="10">
-        <v>2</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="10" t="s">
+    <row r="6" ht="62.4" spans="1:10">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3">
+        <v>46011</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="12">
-        <v>46021</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="I6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="J6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" ht="62.4" spans="1:11">
-      <c r="A6" s="10">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="12">
-        <v>46011</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="87" orientation="landscape"/>
